--- a/manuscript_image/Table_S3.xlsx
+++ b/manuscript_image/Table_S3.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\WatGNN_all\Image\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\WatGNN_SI\manuscript_image\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{09EEEFB5-5116-48FE-8894-0597DC7B13A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB8CA0E6-A0B9-4E30-B52A-C8E477913FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2745" yWindow="2265" windowWidth="28800" windowHeight="11295" xr2:uid="{087B3F5B-CDD3-466A-AE16-1BDF97D4AC1E}"/>
+    <workbookView xWindow="12135" yWindow="2175" windowWidth="18060" windowHeight="11295" xr2:uid="{087B3F5B-CDD3-466A-AE16-1BDF97D4AC1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -114,19 +114,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>7.7±5.5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1–29</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">B-factor &lt;40 Å² ref. water </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>B-factor &lt;40 Å² ref. water within 4 Å of compound atoms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1–22</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.9±4.5</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -798,7 +798,7 @@
         <v>3971</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D2" s="6">
         <v>723047</v>
@@ -890,19 +890,19 @@
         <v>171</v>
       </c>
       <c r="C6" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D6" s="14">
+        <v>1003</v>
+      </c>
+      <c r="E6" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="14">
-        <v>1318</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>21</v>
-      </c>
       <c r="F6" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6" s="15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="17.25" thickTop="1"/>

--- a/manuscript_image/Table_S3.xlsx
+++ b/manuscript_image/Table_S3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\WatGNN_SI\manuscript_image\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB8CA0E6-A0B9-4E30-B52A-C8E477913FD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C113DC53-2004-44A3-BD04-117E655AD54F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12135" yWindow="2175" windowWidth="18060" windowHeight="11295" xr2:uid="{087B3F5B-CDD3-466A-AE16-1BDF97D4AC1E}"/>
+    <workbookView xWindow="17025" yWindow="3000" windowWidth="18060" windowHeight="11295" xr2:uid="{087B3F5B-CDD3-466A-AE16-1BDF97D4AC1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="29">
   <si>
     <t>Dataset</t>
   </si>
@@ -127,6 +127,22 @@
   </si>
   <si>
     <t>5.9±4.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MobyWat</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B-factor &lt;40 Å² ref. water within 3 Å of both receptor and ligand atoms</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>7.6±5.2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2–16</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -328,9 +344,7 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="thick">
         <color auto="1"/>
       </bottom>
@@ -343,9 +357,7 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="thick">
         <color auto="1"/>
       </bottom>
@@ -358,9 +370,7 @@
       <right style="thick">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="thick">
         <color auto="1"/>
       </bottom>
@@ -755,7 +765,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{734974DA-84C9-44DB-B819-D083BAEE9254}">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="10.875" customWidth="1"/>
@@ -882,30 +892,53 @@
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="75.75" thickBot="1">
-      <c r="A6" s="12" t="s">
+    <row r="6" spans="1:7" ht="75">
+      <c r="A6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="9">
         <v>171</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="10">
         <v>1003</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="14">
+      <c r="F6" s="10">
         <v>5</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="11" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="17.25" thickTop="1"/>
+    <row r="7" spans="1:7" ht="90.75" thickBot="1">
+      <c r="A7" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="13">
+        <v>5</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="14">
+        <v>38</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="14">
+        <v>6</v>
+      </c>
+      <c r="G7" s="15" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="17.25" thickTop="1"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/manuscript_image/Table_S3.xlsx
+++ b/manuscript_image/Table_S3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\GitHub\WatGNN_SI\manuscript_image\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C113DC53-2004-44A3-BD04-117E655AD54F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07806350-6E26-4921-80AA-331355C2E90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="17025" yWindow="3000" windowWidth="18060" windowHeight="11295" xr2:uid="{087B3F5B-CDD3-466A-AE16-1BDF97D4AC1E}"/>
+    <workbookView xWindow="19440" yWindow="1440" windowWidth="18060" windowHeight="11295" xr2:uid="{087B3F5B-CDD3-466A-AE16-1BDF97D4AC1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -134,15 +134,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>B-factor &lt;40 Å² ref. water within 3 Å of both receptor and ligand atoms</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>7.6±5.2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>2–16</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>B-factor &lt;40 Å² ref. water within 3.5 Å of both receptor and ligand atoms</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -923,19 +923,19 @@
         <v>5</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="D7" s="14">
         <v>38</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F7" s="14">
         <v>6</v>
       </c>
       <c r="G7" s="15" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="17.25" thickTop="1"/>
